--- a/nirmaan_stack/services/boq_parser/tests/fixtures/synthetic_blank_cols.xlsx
+++ b/nirmaan_stack/services/boq_parser/tests/fixtures/synthetic_blank_cols.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D5"/>
+  <dimension ref="B1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,7 @@
           <t>D1</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
